--- a/cv_data/publications.xlsx
+++ b/cv_data/publications.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/090f7abe46c7f02e/GitHub/ccl_cv/cv_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{3D42CD72-B16F-463A-B69E-48C125EA61AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04FA43C1-EB05-447E-A3AC-B4EDF6735968}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{B0752530-F4C1-48EE-B25C-E0F79B96993A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A6567D4-D459-4560-A98F-764C66F218D2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="136">
   <si>
     <t>type</t>
   </si>
@@ -421,6 +421,18 @@
   </si>
   <si>
     <t>https://ajph.aphapublications.org/doi/10.2105/AJPH.2026.308569</t>
+  </si>
+  <si>
+    <t>Childhood exposure to intimate partner violence and female concealed carry over the life course: A brief report</t>
+  </si>
+  <si>
+    <t>Journal of Family Violence</t>
+  </si>
+  <si>
+    <t>KK O'Neill, CC Lanfear</t>
+  </si>
+  <si>
+    <t>(Conditional accept)</t>
   </si>
 </sst>
 </file>
@@ -803,7 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36.85546875" customWidth="1"/>
@@ -1450,6 +1462,23 @@
       </c>
       <c r="H27" t="s">
         <v>129</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>134</v>
+      </c>
+      <c r="C28" t="s">
+        <v>135</v>
+      </c>
+      <c r="D28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E28" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/cv_data/publications.xlsx
+++ b/cv_data/publications.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/090f7abe46c7f02e/GitHub/ccl_cv/cv_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{B0752530-F4C1-48EE-B25C-E0F79B96993A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A6567D4-D459-4560-A98F-764C66F218D2}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{B0752530-F4C1-48EE-B25C-E0F79B96993A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22011195-D26F-4501-AED1-C4FD86D4E0B5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="140">
   <si>
     <t>type</t>
   </si>
@@ -432,7 +432,19 @@
     <t>KK O'Neill, CC Lanfear</t>
   </si>
   <si>
-    <t>(Conditional accept)</t>
+    <t>(Forthcoming)</t>
+  </si>
+  <si>
+    <t>Life-course processes as cause and effect of macro-level changes in gun violence</t>
+  </si>
+  <si>
+    <t>(Conditional Accept)</t>
+  </si>
+  <si>
+    <t>CC Lanfear, RJ Sampson</t>
+  </si>
+  <si>
+    <t>British Journal of Criminology</t>
   </si>
 </sst>
 </file>
@@ -512,10 +524,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -815,7 +823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36.85546875" customWidth="1"/>
@@ -1479,6 +1487,23 @@
       </c>
       <c r="E28" t="s">
         <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>138</v>
+      </c>
+      <c r="C29" t="s">
+        <v>137</v>
+      </c>
+      <c r="D29" t="s">
+        <v>136</v>
+      </c>
+      <c r="E29" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/cv_data/publications.xlsx
+++ b/cv_data/publications.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/090f7abe46c7f02e/GitHub/ccl_cv/cv_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cl948\OneDrive\GitHub\ccl_cv\cv_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{B0752530-F4C1-48EE-B25C-E0F79B96993A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22011195-D26F-4501-AED1-C4FD86D4E0B5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FAA7A2-9C6C-4387-A86C-690905E7506F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="143">
   <si>
     <t>type</t>
   </si>
@@ -445,6 +445,15 @@
   </si>
   <si>
     <t>British Journal of Criminology</t>
+  </si>
+  <si>
+    <t>DS Kirk, CC Lanfear, DK Humphreys</t>
+  </si>
+  <si>
+    <t>Justice Quarterly</t>
+  </si>
+  <si>
+    <t>Closing the gun show loophole? Evidence on federal firearm licensing and background checks</t>
   </si>
 </sst>
 </file>
@@ -823,17 +832,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H30"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="4" max="4" width="65.28515625" customWidth="1"/>
-    <col min="5" max="5" width="34.42578125" customWidth="1"/>
-    <col min="6" max="6" width="42.42578125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="26.5703125" customWidth="1"/>
+    <col min="2" max="2" width="36.81640625" customWidth="1"/>
+    <col min="4" max="4" width="65.26953125" customWidth="1"/>
+    <col min="5" max="5" width="34.453125" customWidth="1"/>
+    <col min="6" max="6" width="42.453125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="26.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -859,7 +868,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -885,7 +894,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -911,7 +920,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -937,7 +946,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -963,7 +972,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -989,7 +998,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1015,7 +1024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -1032,7 +1041,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -1049,7 +1058,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1066,7 +1075,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1083,7 +1092,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1103,7 +1112,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1126,7 +1135,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1152,7 +1161,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1178,7 +1187,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1201,7 +1210,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1218,7 +1227,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -1244,7 +1253,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -1270,7 +1279,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -1293,7 +1302,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -1319,7 +1328,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -1342,7 +1351,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1368,7 +1377,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -1394,7 +1403,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -1420,7 +1429,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -1446,7 +1455,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -1472,7 +1481,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -1489,7 +1498,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>7</v>
       </c>
@@ -1504,6 +1513,23 @@
       </c>
       <c r="E29" t="s">
         <v>139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
+        <v>140</v>
+      </c>
+      <c r="C30" t="s">
+        <v>137</v>
+      </c>
+      <c r="D30" t="s">
+        <v>142</v>
+      </c>
+      <c r="E30" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
